--- a/liaisons_Super_Constellation/Reseau_Eastern_Air_Lines_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Eastern_Air_Lines_L1049_sourced.xlsx
@@ -884,6 +884,33 @@
       <c r="A16" t="str">
         <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
       </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1016,25 +1043,145 @@
       <c r="A5" t="str">
         <v/>
       </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>Notes :</v>
       </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>[S] Sourcé : la liaison Miami–La Havane figurait parmi les rares routes internationales régulières d'Eastern à l'époque.</v>
       </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>[R] Reconstitué : numéros de vol et horaires.</v>
       </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>HL : Heure Locale.</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
